--- a/data/extracted/inventory-receipts/CONTENEDOR TELA GOLDEN TOUCH  27 MARZO.xlsx
+++ b/data/extracted/inventory-receipts/CONTENEDOR TELA GOLDEN TOUCH  27 MARZO.xlsx
@@ -1,18 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AF0036-DESKTOP\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\txpacifico\txp-inventory\data\extracted\inventory-receipts\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B55855-9570-4633-A538-96ABDFFF4C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10080" windowHeight="9465"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="IBUM" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -3578,7 +3580,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="###,###,###,###,##0.#0"/>
   </numFmts>
@@ -3619,12 +3621,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3904,50 +3905,50 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L927"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="1" customWidth="1"/>
-    <col min="8" max="12" width="10.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="3.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="1" customWidth="1"/>
+    <col min="8" max="12" width="10.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -3985,12 +3986,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -4028,7 +4029,7 @@
         <v>97.7</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F8" s="1" t="s">
         <v>27</v>
       </c>
@@ -4048,7 +4049,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F9" s="1" t="s">
         <v>29</v>
       </c>
@@ -4068,7 +4069,7 @@
         <v>97.7</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -4106,7 +4107,7 @@
         <v>163.5</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F11" s="1" t="s">
         <v>27</v>
       </c>
@@ -4126,7 +4127,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F12" s="1" t="s">
         <v>29</v>
       </c>
@@ -4146,7 +4147,7 @@
         <v>163.5</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -4184,7 +4185,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F14" s="1" t="s">
         <v>27</v>
       </c>
@@ -4204,7 +4205,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F15" s="1" t="s">
         <v>29</v>
       </c>
@@ -4224,7 +4225,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -4262,7 +4263,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F17" s="1" t="s">
         <v>27</v>
       </c>
@@ -4282,7 +4283,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F18" s="1" t="s">
         <v>29</v>
       </c>
@@ -4302,7 +4303,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
@@ -4340,7 +4341,7 @@
         <v>145.1</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F20" s="1" t="s">
         <v>27</v>
       </c>
@@ -4360,7 +4361,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F21" s="1" t="s">
         <v>29</v>
       </c>
@@ -4380,7 +4381,7 @@
         <v>145.1</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
@@ -4418,7 +4419,7 @@
         <v>162.9</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F23" s="1" t="s">
         <v>27</v>
       </c>
@@ -4438,7 +4439,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F24" s="1" t="s">
         <v>29</v>
       </c>
@@ -4458,7 +4459,7 @@
         <v>162.9</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>19</v>
       </c>
@@ -4496,7 +4497,7 @@
         <v>362.2</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F26" s="1" t="s">
         <v>27</v>
       </c>
@@ -4516,7 +4517,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F27" s="1" t="s">
         <v>29</v>
       </c>
@@ -4536,7 +4537,7 @@
         <v>362.2</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>19</v>
       </c>
@@ -4574,7 +4575,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F29" s="1" t="s">
         <v>27</v>
       </c>
@@ -4594,7 +4595,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F30" s="1" t="s">
         <v>29</v>
       </c>
@@ -4614,7 +4615,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>19</v>
       </c>
@@ -4652,7 +4653,7 @@
         <v>66.8</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F32" s="1" t="s">
         <v>27</v>
       </c>
@@ -4672,7 +4673,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F33" s="1" t="s">
         <v>29</v>
       </c>
@@ -4692,7 +4693,7 @@
         <v>66.8</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>19</v>
       </c>
@@ -4730,7 +4731,7 @@
         <v>35.799999999999997</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F35" s="1" t="s">
         <v>27</v>
       </c>
@@ -4750,7 +4751,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F36" s="1" t="s">
         <v>29</v>
       </c>
@@ -4770,7 +4771,7 @@
         <v>35.799999999999997</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>19</v>
       </c>
@@ -4808,7 +4809,7 @@
         <v>68.5</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F38" s="1" t="s">
         <v>27</v>
       </c>
@@ -4828,7 +4829,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F39" s="1" t="s">
         <v>29</v>
       </c>
@@ -4848,7 +4849,7 @@
         <v>68.5</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F40" s="1" t="s">
         <v>27</v>
       </c>
@@ -4868,7 +4869,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F41" s="1" t="s">
         <v>70</v>
       </c>
@@ -4888,7 +4889,7 @@
         <v>1182.9000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>71</v>
       </c>
@@ -4926,7 +4927,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>71</v>
       </c>
@@ -4964,7 +4965,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>71</v>
       </c>
@@ -5002,7 +5003,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>71</v>
       </c>
@@ -5040,7 +5041,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>71</v>
       </c>
@@ -5078,7 +5079,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>71</v>
       </c>
@@ -5116,7 +5117,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>71</v>
       </c>
@@ -5154,7 +5155,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>71</v>
       </c>
@@ -5192,7 +5193,7 @@
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>71</v>
       </c>
@@ -5230,7 +5231,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>71</v>
       </c>
@@ -5268,7 +5269,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>71</v>
       </c>
@@ -5306,7 +5307,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>71</v>
       </c>
@@ -5344,7 +5345,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>71</v>
       </c>
@@ -5382,7 +5383,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>71</v>
       </c>
@@ -5420,7 +5421,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>71</v>
       </c>
@@ -5458,7 +5459,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>71</v>
       </c>
@@ -5496,7 +5497,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>71</v>
       </c>
@@ -5534,7 +5535,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>71</v>
       </c>
@@ -5572,7 +5573,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>71</v>
       </c>
@@ -5610,7 +5611,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>71</v>
       </c>
@@ -5648,7 +5649,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>71</v>
       </c>
@@ -5686,7 +5687,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>71</v>
       </c>
@@ -5724,7 +5725,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>71</v>
       </c>
@@ -5762,7 +5763,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>71</v>
       </c>
@@ -5800,7 +5801,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>71</v>
       </c>
@@ -5838,7 +5839,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>71</v>
       </c>
@@ -5876,7 +5877,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>71</v>
       </c>
@@ -5914,7 +5915,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>71</v>
       </c>
@@ -5952,7 +5953,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>71</v>
       </c>
@@ -5990,7 +5991,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>71</v>
       </c>
@@ -6028,7 +6029,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>71</v>
       </c>
@@ -6066,7 +6067,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>71</v>
       </c>
@@ -6104,7 +6105,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>71</v>
       </c>
@@ -6142,7 +6143,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>71</v>
       </c>
@@ -6180,7 +6181,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>71</v>
       </c>
@@ -6218,7 +6219,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>71</v>
       </c>
@@ -6256,7 +6257,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>71</v>
       </c>
@@ -6294,7 +6295,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>71</v>
       </c>
@@ -6332,7 +6333,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>71</v>
       </c>
@@ -6370,7 +6371,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>71</v>
       </c>
@@ -6408,7 +6409,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6446,7 +6447,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>71</v>
       </c>
@@ -6484,7 +6485,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>71</v>
       </c>
@@ -6522,7 +6523,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>71</v>
       </c>
@@ -6560,7 +6561,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>71</v>
       </c>
@@ -6598,7 +6599,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>71</v>
       </c>
@@ -6636,7 +6637,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>71</v>
       </c>
@@ -6674,7 +6675,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>71</v>
       </c>
@@ -6712,7 +6713,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>71</v>
       </c>
@@ -6750,7 +6751,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>71</v>
       </c>
@@ -6788,7 +6789,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>71</v>
       </c>
@@ -6826,7 +6827,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>71</v>
       </c>
@@ -6864,7 +6865,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>71</v>
       </c>
@@ -6902,7 +6903,7 @@
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>71</v>
       </c>
@@ -6940,7 +6941,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>71</v>
       </c>
@@ -6978,7 +6979,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>71</v>
       </c>
@@ -7016,7 +7017,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>71</v>
       </c>
@@ -7054,7 +7055,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>71</v>
       </c>
@@ -7092,7 +7093,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>71</v>
       </c>
@@ -7130,7 +7131,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>71</v>
       </c>
@@ -7168,7 +7169,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>71</v>
       </c>
@@ -7206,7 +7207,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>71</v>
       </c>
@@ -7244,7 +7245,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>71</v>
       </c>
@@ -7282,7 +7283,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>71</v>
       </c>
@@ -7320,7 +7321,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>71</v>
       </c>
@@ -7358,7 +7359,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>71</v>
       </c>
@@ -7396,7 +7397,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>71</v>
       </c>
@@ -7434,7 +7435,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>71</v>
       </c>
@@ -7472,7 +7473,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>71</v>
       </c>
@@ -7510,7 +7511,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>71</v>
       </c>
@@ -7548,7 +7549,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>71</v>
       </c>
@@ -7586,7 +7587,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>71</v>
       </c>
@@ -7624,7 +7625,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>71</v>
       </c>
@@ -7662,7 +7663,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>71</v>
       </c>
@@ -7700,7 +7701,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>71</v>
       </c>
@@ -7738,7 +7739,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>71</v>
       </c>
@@ -7776,7 +7777,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>71</v>
       </c>
@@ -7814,7 +7815,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F119" s="1" t="s">
         <v>27</v>
       </c>
@@ -7834,7 +7835,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F120" s="1" t="s">
         <v>217</v>
       </c>
@@ -7854,7 +7855,7 @@
         <v>1709.7</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>71</v>
       </c>
@@ -7892,7 +7893,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>71</v>
       </c>
@@ -7930,7 +7931,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>71</v>
       </c>
@@ -7968,7 +7969,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>71</v>
       </c>
@@ -8006,7 +8007,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>71</v>
       </c>
@@ -8044,7 +8045,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>71</v>
       </c>
@@ -8082,7 +8083,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>71</v>
       </c>
@@ -8120,7 +8121,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>71</v>
       </c>
@@ -8158,7 +8159,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>71</v>
       </c>
@@ -8196,7 +8197,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>71</v>
       </c>
@@ -8234,7 +8235,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>71</v>
       </c>
@@ -8272,7 +8273,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>71</v>
       </c>
@@ -8310,7 +8311,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>71</v>
       </c>
@@ -8348,7 +8349,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>71</v>
       </c>
@@ -8386,7 +8387,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>71</v>
       </c>
@@ -8424,7 +8425,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>71</v>
       </c>
@@ -8462,7 +8463,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>71</v>
       </c>
@@ -8500,7 +8501,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>71</v>
       </c>
@@ -8538,7 +8539,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>71</v>
       </c>
@@ -8576,7 +8577,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>71</v>
       </c>
@@ -8614,7 +8615,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>71</v>
       </c>
@@ -8652,7 +8653,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>71</v>
       </c>
@@ -8690,7 +8691,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>71</v>
       </c>
@@ -8728,7 +8729,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>71</v>
       </c>
@@ -8766,7 +8767,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>71</v>
       </c>
@@ -8804,7 +8805,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>71</v>
       </c>
@@ -8842,7 +8843,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>71</v>
       </c>
@@ -8880,7 +8881,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>71</v>
       </c>
@@ -8918,7 +8919,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>71</v>
       </c>
@@ -8956,7 +8957,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>71</v>
       </c>
@@ -8994,7 +8995,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>71</v>
       </c>
@@ -9032,7 +9033,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>71</v>
       </c>
@@ -9070,7 +9071,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
         <v>71</v>
       </c>
@@ -9108,7 +9109,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>71</v>
       </c>
@@ -9146,7 +9147,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>71</v>
       </c>
@@ -9184,7 +9185,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
         <v>71</v>
       </c>
@@ -9222,7 +9223,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>71</v>
       </c>
@@ -9260,7 +9261,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>71</v>
       </c>
@@ -9298,7 +9299,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
         <v>71</v>
       </c>
@@ -9336,7 +9337,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
         <v>71</v>
       </c>
@@ -9374,7 +9375,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>71</v>
       </c>
@@ -9412,7 +9413,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
         <v>71</v>
       </c>
@@ -9450,7 +9451,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
         <v>71</v>
       </c>
@@ -9488,7 +9489,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
         <v>71</v>
       </c>
@@ -9526,7 +9527,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
         <v>71</v>
       </c>
@@ -9564,7 +9565,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
         <v>71</v>
       </c>
@@ -9602,7 +9603,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>71</v>
       </c>
@@ -9640,7 +9641,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
         <v>71</v>
       </c>
@@ -9678,7 +9679,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
         <v>71</v>
       </c>
@@ -9716,7 +9717,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
         <v>71</v>
       </c>
@@ -9754,7 +9755,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
         <v>71</v>
       </c>
@@ -9792,7 +9793,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
         <v>71</v>
       </c>
@@ -9830,7 +9831,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
         <v>71</v>
       </c>
@@ -9868,7 +9869,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
         <v>71</v>
       </c>
@@ -9906,7 +9907,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
         <v>71</v>
       </c>
@@ -9944,7 +9945,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
         <v>71</v>
       </c>
@@ -9982,7 +9983,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
         <v>71</v>
       </c>
@@ -10020,7 +10021,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
         <v>71</v>
       </c>
@@ -10058,7 +10059,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
         <v>71</v>
       </c>
@@ -10096,7 +10097,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
         <v>71</v>
       </c>
@@ -10134,7 +10135,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
         <v>71</v>
       </c>
@@ -10172,7 +10173,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
         <v>71</v>
       </c>
@@ -10210,7 +10211,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
         <v>71</v>
       </c>
@@ -10248,7 +10249,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
         <v>71</v>
       </c>
@@ -10286,7 +10287,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
         <v>71</v>
       </c>
@@ -10324,7 +10325,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
         <v>71</v>
       </c>
@@ -10362,7 +10363,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
         <v>71</v>
       </c>
@@ -10400,7 +10401,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
         <v>71</v>
       </c>
@@ -10438,7 +10439,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
         <v>71</v>
       </c>
@@ -10476,7 +10477,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
         <v>71</v>
       </c>
@@ -10514,7 +10515,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
         <v>71</v>
       </c>
@@ -10552,7 +10553,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
         <v>71</v>
       </c>
@@ -10590,7 +10591,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
         <v>71</v>
       </c>
@@ -10628,7 +10629,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
         <v>71</v>
       </c>
@@ -10666,7 +10667,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
         <v>71</v>
       </c>
@@ -10704,7 +10705,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
         <v>71</v>
       </c>
@@ -10742,7 +10743,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
         <v>71</v>
       </c>
@@ -10780,7 +10781,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
         <v>71</v>
       </c>
@@ -10818,7 +10819,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
         <v>71</v>
       </c>
@@ -10856,7 +10857,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
         <v>71</v>
       </c>
@@ -10894,7 +10895,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
         <v>71</v>
       </c>
@@ -10932,7 +10933,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
         <v>71</v>
       </c>
@@ -10970,7 +10971,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
         <v>71</v>
       </c>
@@ -11008,7 +11009,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
         <v>71</v>
       </c>
@@ -11046,7 +11047,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
         <v>71</v>
       </c>
@@ -11084,7 +11085,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
         <v>71</v>
       </c>
@@ -11122,7 +11123,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
         <v>71</v>
       </c>
@@ -11160,7 +11161,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
         <v>71</v>
       </c>
@@ -11198,7 +11199,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
         <v>71</v>
       </c>
@@ -11236,7 +11237,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
         <v>71</v>
       </c>
@@ -11274,7 +11275,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
         <v>71</v>
       </c>
@@ -11312,7 +11313,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
         <v>71</v>
       </c>
@@ -11350,7 +11351,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
         <v>71</v>
       </c>
@@ -11388,7 +11389,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
         <v>71</v>
       </c>
@@ -11426,7 +11427,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
         <v>71</v>
       </c>
@@ -11464,7 +11465,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
         <v>71</v>
       </c>
@@ -11502,7 +11503,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
         <v>71</v>
       </c>
@@ -11540,7 +11541,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
         <v>71</v>
       </c>
@@ -11578,7 +11579,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
         <v>71</v>
       </c>
@@ -11616,7 +11617,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
         <v>71</v>
       </c>
@@ -11654,7 +11655,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
         <v>71</v>
       </c>
@@ -11692,7 +11693,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
         <v>71</v>
       </c>
@@ -11730,7 +11731,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="s">
         <v>71</v>
       </c>
@@ -11768,7 +11769,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
         <v>71</v>
       </c>
@@ -11806,7 +11807,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
         <v>71</v>
       </c>
@@ -11844,7 +11845,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
         <v>71</v>
       </c>
@@ -11882,7 +11883,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
         <v>71</v>
       </c>
@@ -11920,7 +11921,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
         <v>71</v>
       </c>
@@ -11958,7 +11959,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
         <v>71</v>
       </c>
@@ -11996,7 +11997,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
         <v>71</v>
       </c>
@@ -12034,7 +12035,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="s">
         <v>71</v>
       </c>
@@ -12072,7 +12073,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
         <v>71</v>
       </c>
@@ -12110,7 +12111,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="s">
         <v>71</v>
       </c>
@@ -12148,7 +12149,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
         <v>71</v>
       </c>
@@ -12186,7 +12187,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
         <v>71</v>
       </c>
@@ -12224,7 +12225,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
         <v>71</v>
       </c>
@@ -12262,7 +12263,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="s">
         <v>71</v>
       </c>
@@ -12300,7 +12301,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
         <v>71</v>
       </c>
@@ -12338,7 +12339,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="s">
         <v>71</v>
       </c>
@@ -12376,7 +12377,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
         <v>71</v>
       </c>
@@ -12414,7 +12415,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
         <v>71</v>
       </c>
@@ -12452,7 +12453,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
         <v>71</v>
       </c>
@@ -12490,7 +12491,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
         <v>71</v>
       </c>
@@ -12528,7 +12529,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F244" s="1" t="s">
         <v>27</v>
       </c>
@@ -12548,7 +12549,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F245" s="1" t="s">
         <v>388</v>
       </c>
@@ -12568,7 +12569,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
         <v>71</v>
       </c>
@@ -12606,7 +12607,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="s">
         <v>71</v>
       </c>
@@ -12644,7 +12645,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
         <v>71</v>
       </c>
@@ -12682,7 +12683,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
         <v>71</v>
       </c>
@@ -12720,7 +12721,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
         <v>71</v>
       </c>
@@ -12758,7 +12759,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
         <v>71</v>
       </c>
@@ -12796,7 +12797,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
         <v>71</v>
       </c>
@@ -12834,7 +12835,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
         <v>71</v>
       </c>
@@ -12872,7 +12873,7 @@
         <v>28.4</v>
       </c>
     </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
         <v>71</v>
       </c>
@@ -12910,7 +12911,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
         <v>71</v>
       </c>
@@ -12948,7 +12949,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
         <v>71</v>
       </c>
@@ -12986,7 +12987,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
         <v>71</v>
       </c>
@@ -13024,7 +13025,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
         <v>71</v>
       </c>
@@ -13062,7 +13063,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" s="1" t="s">
         <v>71</v>
       </c>
@@ -13100,7 +13101,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
         <v>71</v>
       </c>
@@ -13138,7 +13139,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="s">
         <v>71</v>
       </c>
@@ -13176,7 +13177,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
         <v>71</v>
       </c>
@@ -13214,7 +13215,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="s">
         <v>71</v>
       </c>
@@ -13252,7 +13253,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
         <v>71</v>
       </c>
@@ -13290,7 +13291,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="s">
         <v>71</v>
       </c>
@@ -13328,7 +13329,7 @@
         <v>32.1</v>
       </c>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
         <v>71</v>
       </c>
@@ -13366,7 +13367,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" s="1" t="s">
         <v>71</v>
       </c>
@@ -13404,7 +13405,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F268" s="1" t="s">
         <v>27</v>
       </c>
@@ -13424,7 +13425,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F269" s="1" t="s">
         <v>412</v>
       </c>
@@ -13444,7 +13445,7 @@
         <v>491.7</v>
       </c>
     </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
         <v>71</v>
       </c>
@@ -13482,7 +13483,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="s">
         <v>71</v>
       </c>
@@ -13520,7 +13521,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
         <v>71</v>
       </c>
@@ -13558,7 +13559,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A273" s="1" t="s">
         <v>71</v>
       </c>
@@ -13596,7 +13597,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
         <v>71</v>
       </c>
@@ -13634,7 +13635,7 @@
         <v>17.7</v>
       </c>
     </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A275" s="1" t="s">
         <v>71</v>
       </c>
@@ -13672,7 +13673,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
         <v>71</v>
       </c>
@@ -13710,7 +13711,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A277" s="1" t="s">
         <v>71</v>
       </c>
@@ -13748,7 +13749,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
         <v>71</v>
       </c>
@@ -13786,7 +13787,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A279" s="1" t="s">
         <v>71</v>
       </c>
@@ -13824,7 +13825,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
         <v>71</v>
       </c>
@@ -13862,7 +13863,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A281" s="1" t="s">
         <v>71</v>
       </c>
@@ -13900,7 +13901,7 @@
         <v>28.8</v>
       </c>
     </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
         <v>71</v>
       </c>
@@ -13938,7 +13939,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A283" s="1" t="s">
         <v>71</v>
       </c>
@@ -13976,7 +13977,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
         <v>71</v>
       </c>
@@ -14014,7 +14015,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="s">
         <v>71</v>
       </c>
@@ -14052,7 +14053,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
         <v>71</v>
       </c>
@@ -14090,7 +14091,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="s">
         <v>71</v>
       </c>
@@ -14128,7 +14129,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
         <v>71</v>
       </c>
@@ -14166,7 +14167,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="289" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="s">
         <v>71</v>
       </c>
@@ -14204,7 +14205,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
         <v>71</v>
       </c>
@@ -14242,7 +14243,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="s">
         <v>71</v>
       </c>
@@ -14280,7 +14281,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F292" s="1" t="s">
         <v>27</v>
       </c>
@@ -14300,7 +14301,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="293" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F293" s="1" t="s">
         <v>412</v>
       </c>
@@ -14320,7 +14321,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
         <v>71</v>
       </c>
@@ -14358,7 +14359,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
         <v>71</v>
       </c>
@@ -14396,7 +14397,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
         <v>71</v>
       </c>
@@ -14434,7 +14435,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="297" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="s">
         <v>71</v>
       </c>
@@ -14472,7 +14473,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="298" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
         <v>71</v>
       </c>
@@ -14510,7 +14511,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="299" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A299" s="1" t="s">
         <v>71</v>
       </c>
@@ -14548,7 +14549,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="300" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
         <v>71</v>
       </c>
@@ -14586,7 +14587,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A301" s="1" t="s">
         <v>71</v>
       </c>
@@ -14624,7 +14625,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="302" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
         <v>71</v>
       </c>
@@ -14662,7 +14663,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="303" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A303" s="1" t="s">
         <v>71</v>
       </c>
@@ -14700,7 +14701,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="304" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
         <v>71</v>
       </c>
@@ -14738,7 +14739,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A305" s="1" t="s">
         <v>71</v>
       </c>
@@ -14776,7 +14777,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
         <v>71</v>
       </c>
@@ -14814,7 +14815,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A307" s="1" t="s">
         <v>71</v>
       </c>
@@ -14852,7 +14853,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
         <v>71</v>
       </c>
@@ -14890,7 +14891,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A309" s="1" t="s">
         <v>71</v>
       </c>
@@ -14928,7 +14929,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
         <v>71</v>
       </c>
@@ -14966,7 +14967,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="s">
         <v>71</v>
       </c>
@@ -15004,7 +15005,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
         <v>71</v>
       </c>
@@ -15042,7 +15043,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="s">
         <v>71</v>
       </c>
@@ -15080,7 +15081,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
         <v>71</v>
       </c>
@@ -15118,7 +15119,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A315" s="1" t="s">
         <v>71</v>
       </c>
@@ -15156,7 +15157,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="s">
         <v>71</v>
       </c>
@@ -15194,7 +15195,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A317" s="1" t="s">
         <v>71</v>
       </c>
@@ -15232,7 +15233,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
         <v>71</v>
       </c>
@@ -15270,7 +15271,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A319" s="1" t="s">
         <v>71</v>
       </c>
@@ -15308,7 +15309,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
         <v>71</v>
       </c>
@@ -15346,7 +15347,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="321" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A321" s="1" t="s">
         <v>71</v>
       </c>
@@ -15384,7 +15385,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="322" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
         <v>71</v>
       </c>
@@ -15422,7 +15423,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="323" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A323" s="1" t="s">
         <v>71</v>
       </c>
@@ -15460,7 +15461,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="324" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
         <v>71</v>
       </c>
@@ -15498,7 +15499,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="325" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A325" s="1" t="s">
         <v>71</v>
       </c>
@@ -15536,7 +15537,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="326" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
         <v>71</v>
       </c>
@@ -15574,7 +15575,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="327" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A327" s="1" t="s">
         <v>71</v>
       </c>
@@ -15612,7 +15613,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="328" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
         <v>71</v>
       </c>
@@ -15650,7 +15651,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="329" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="s">
         <v>71</v>
       </c>
@@ -15688,7 +15689,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="330" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
         <v>71</v>
       </c>
@@ -15726,7 +15727,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="331" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A331" s="1" t="s">
         <v>71</v>
       </c>
@@ -15764,7 +15765,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="332" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
         <v>71</v>
       </c>
@@ -15802,7 +15803,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="333" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A333" s="1" t="s">
         <v>71</v>
       </c>
@@ -15840,7 +15841,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="334" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
         <v>71</v>
       </c>
@@ -15878,7 +15879,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="335" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A335" s="1" t="s">
         <v>71</v>
       </c>
@@ -15916,7 +15917,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="336" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
         <v>71</v>
       </c>
@@ -15954,7 +15955,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="337" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A337" s="1" t="s">
         <v>71</v>
       </c>
@@ -15992,7 +15993,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="338" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
         <v>71</v>
       </c>
@@ -16030,7 +16031,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="339" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A339" s="1" t="s">
         <v>71</v>
       </c>
@@ -16068,7 +16069,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="340" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
         <v>71</v>
       </c>
@@ -16106,7 +16107,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="341" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A341" s="1" t="s">
         <v>71</v>
       </c>
@@ -16144,7 +16145,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="342" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
         <v>71</v>
       </c>
@@ -16182,7 +16183,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="343" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A343" s="1" t="s">
         <v>71</v>
       </c>
@@ -16220,7 +16221,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="344" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
         <v>71</v>
       </c>
@@ -16258,7 +16259,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="345" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A345" s="1" t="s">
         <v>71</v>
       </c>
@@ -16296,7 +16297,7 @@
         <v>30.2</v>
       </c>
     </row>
-    <row r="346" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
         <v>71</v>
       </c>
@@ -16334,7 +16335,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="347" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A347" s="1" t="s">
         <v>71</v>
       </c>
@@ -16372,7 +16373,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="348" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
         <v>71</v>
       </c>
@@ -16410,7 +16411,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="349" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A349" s="1" t="s">
         <v>71</v>
       </c>
@@ -16448,7 +16449,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="350" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="s">
         <v>71</v>
       </c>
@@ -16486,7 +16487,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="351" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A351" s="1" t="s">
         <v>71</v>
       </c>
@@ -16524,7 +16525,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="352" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
         <v>71</v>
       </c>
@@ -16562,7 +16563,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="353" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A353" s="1" t="s">
         <v>71</v>
       </c>
@@ -16600,7 +16601,7 @@
         <v>17.8</v>
       </c>
     </row>
-    <row r="354" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="s">
         <v>71</v>
       </c>
@@ -16638,7 +16639,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="355" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A355" s="1" t="s">
         <v>71</v>
       </c>
@@ -16676,7 +16677,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="356" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="s">
         <v>71</v>
       </c>
@@ -16714,7 +16715,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="357" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A357" s="1" t="s">
         <v>71</v>
       </c>
@@ -16752,7 +16753,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="358" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
         <v>71</v>
       </c>
@@ -16790,7 +16791,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="359" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A359" s="1" t="s">
         <v>71</v>
       </c>
@@ -16828,7 +16829,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="360" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
         <v>71</v>
       </c>
@@ -16866,7 +16867,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="361" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A361" s="1" t="s">
         <v>71</v>
       </c>
@@ -16904,7 +16905,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="362" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
         <v>71</v>
       </c>
@@ -16942,7 +16943,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="363" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A363" s="1" t="s">
         <v>71</v>
       </c>
@@ -16980,7 +16981,7 @@
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="364" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="s">
         <v>71</v>
       </c>
@@ -17018,7 +17019,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="365" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A365" s="1" t="s">
         <v>71</v>
       </c>
@@ -17056,7 +17057,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="366" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="s">
         <v>71</v>
       </c>
@@ -17094,7 +17095,7 @@
         <v>28.7</v>
       </c>
     </row>
-    <row r="367" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A367" s="1" t="s">
         <v>71</v>
       </c>
@@ -17132,7 +17133,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="368" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="s">
         <v>71</v>
       </c>
@@ -17170,7 +17171,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="369" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A369" s="1" t="s">
         <v>71</v>
       </c>
@@ -17208,7 +17209,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="370" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="s">
         <v>71</v>
       </c>
@@ -17246,7 +17247,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="371" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A371" s="1" t="s">
         <v>71</v>
       </c>
@@ -17284,7 +17285,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="372" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="s">
         <v>71</v>
       </c>
@@ -17322,7 +17323,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="373" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A373" s="1" t="s">
         <v>71</v>
       </c>
@@ -17360,7 +17361,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="374" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="s">
         <v>71</v>
       </c>
@@ -17398,7 +17399,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="375" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A375" s="1" t="s">
         <v>71</v>
       </c>
@@ -17436,7 +17437,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="376" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="s">
         <v>71</v>
       </c>
@@ -17474,7 +17475,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="377" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A377" s="1" t="s">
         <v>71</v>
       </c>
@@ -17512,7 +17513,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="378" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="s">
         <v>71</v>
       </c>
@@ -17550,7 +17551,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="379" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A379" s="1" t="s">
         <v>71</v>
       </c>
@@ -17588,7 +17589,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="380" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="s">
         <v>71</v>
       </c>
@@ -17626,7 +17627,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="381" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A381" s="1" t="s">
         <v>71</v>
       </c>
@@ -17664,7 +17665,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="382" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="s">
         <v>71</v>
       </c>
@@ -17702,7 +17703,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="383" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A383" s="1" t="s">
         <v>71</v>
       </c>
@@ -17740,7 +17741,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="384" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="s">
         <v>71</v>
       </c>
@@ -17778,7 +17779,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="385" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A385" s="1" t="s">
         <v>71</v>
       </c>
@@ -17816,7 +17817,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="386" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
         <v>71</v>
       </c>
@@ -17854,7 +17855,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="387" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A387" s="1" t="s">
         <v>71</v>
       </c>
@@ -17892,7 +17893,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="388" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
         <v>71</v>
       </c>
@@ -17930,7 +17931,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="389" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A389" s="1" t="s">
         <v>71</v>
       </c>
@@ -17968,7 +17969,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="390" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="s">
         <v>71</v>
       </c>
@@ -18006,7 +18007,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="391" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A391" s="1" t="s">
         <v>71</v>
       </c>
@@ -18044,7 +18045,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="392" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
         <v>71</v>
       </c>
@@ -18082,7 +18083,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="393" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A393" s="1" t="s">
         <v>71</v>
       </c>
@@ -18120,7 +18121,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="394" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
         <v>71</v>
       </c>
@@ -18158,7 +18159,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="395" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A395" s="1" t="s">
         <v>71</v>
       </c>
@@ -18196,7 +18197,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="396" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
         <v>71</v>
       </c>
@@ -18234,7 +18235,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="397" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A397" s="1" t="s">
         <v>71</v>
       </c>
@@ -18272,7 +18273,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="398" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
         <v>71</v>
       </c>
@@ -18310,7 +18311,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="399" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A399" s="1" t="s">
         <v>71</v>
       </c>
@@ -18348,7 +18349,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="400" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="s">
         <v>71</v>
       </c>
@@ -18386,7 +18387,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="401" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A401" s="1" t="s">
         <v>71</v>
       </c>
@@ -18424,7 +18425,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="402" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="s">
         <v>71</v>
       </c>
@@ -18462,7 +18463,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="403" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A403" s="1" t="s">
         <v>71</v>
       </c>
@@ -18500,7 +18501,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="404" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="s">
         <v>71</v>
       </c>
@@ -18538,7 +18539,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="405" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A405" s="1" t="s">
         <v>71</v>
       </c>
@@ -18576,7 +18577,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="406" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="s">
         <v>71</v>
       </c>
@@ -18614,7 +18615,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="407" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A407" s="1" t="s">
         <v>71</v>
       </c>
@@ -18652,7 +18653,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="408" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="s">
         <v>71</v>
       </c>
@@ -18690,7 +18691,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="409" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A409" s="1" t="s">
         <v>71</v>
       </c>
@@ -18728,7 +18729,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="410" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="s">
         <v>71</v>
       </c>
@@ -18766,7 +18767,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="411" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A411" s="1" t="s">
         <v>71</v>
       </c>
@@ -18804,7 +18805,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="412" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="s">
         <v>71</v>
       </c>
@@ -18842,7 +18843,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="413" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A413" s="1" t="s">
         <v>71</v>
       </c>
@@ -18880,7 +18881,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="414" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="s">
         <v>71</v>
       </c>
@@ -18918,7 +18919,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="415" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F415" s="1" t="s">
         <v>27</v>
       </c>
@@ -18938,7 +18939,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="416" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F416" s="1" t="s">
         <v>558</v>
       </c>
@@ -18958,7 +18959,7 @@
         <v>2710.8</v>
       </c>
     </row>
-    <row r="417" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A417" s="1" t="s">
         <v>71</v>
       </c>
@@ -18996,7 +18997,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="418" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="s">
         <v>71</v>
       </c>
@@ -19034,7 +19035,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="419" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A419" s="1" t="s">
         <v>71</v>
       </c>
@@ -19072,7 +19073,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="420" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="s">
         <v>71</v>
       </c>
@@ -19110,7 +19111,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="421" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A421" s="1" t="s">
         <v>71</v>
       </c>
@@ -19148,7 +19149,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="422" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="s">
         <v>71</v>
       </c>
@@ -19186,7 +19187,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="423" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A423" s="1" t="s">
         <v>71</v>
       </c>
@@ -19224,7 +19225,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="424" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="s">
         <v>71</v>
       </c>
@@ -19262,7 +19263,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="425" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A425" s="1" t="s">
         <v>71</v>
       </c>
@@ -19300,7 +19301,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="426" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="s">
         <v>71</v>
       </c>
@@ -19338,7 +19339,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="427" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A427" s="1" t="s">
         <v>71</v>
       </c>
@@ -19376,7 +19377,7 @@
         <v>17.8</v>
       </c>
     </row>
-    <row r="428" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="s">
         <v>71</v>
       </c>
@@ -19414,7 +19415,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="429" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A429" s="1" t="s">
         <v>71</v>
       </c>
@@ -19452,7 +19453,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="430" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="s">
         <v>71</v>
       </c>
@@ -19490,7 +19491,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="431" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A431" s="1" t="s">
         <v>71</v>
       </c>
@@ -19528,7 +19529,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="432" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="s">
         <v>71</v>
       </c>
@@ -19566,7 +19567,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="433" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A433" s="1" t="s">
         <v>71</v>
       </c>
@@ -19604,7 +19605,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="434" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="s">
         <v>71</v>
       </c>
@@ -19642,7 +19643,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="435" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A435" s="1" t="s">
         <v>71</v>
       </c>
@@ -19680,7 +19681,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="436" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="s">
         <v>71</v>
       </c>
@@ -19718,7 +19719,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="437" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A437" s="1" t="s">
         <v>71</v>
       </c>
@@ -19756,7 +19757,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="438" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A438" s="1" t="s">
         <v>71</v>
       </c>
@@ -19794,7 +19795,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="439" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A439" s="1" t="s">
         <v>71</v>
       </c>
@@ -19832,7 +19833,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="440" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A440" s="1" t="s">
         <v>71</v>
       </c>
@@ -19870,7 +19871,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="441" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A441" s="1" t="s">
         <v>71</v>
       </c>
@@ -19908,7 +19909,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="442" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A442" s="1" t="s">
         <v>71</v>
       </c>
@@ -19946,7 +19947,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="443" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A443" s="1" t="s">
         <v>71</v>
       </c>
@@ -19984,7 +19985,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="444" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A444" s="1" t="s">
         <v>71</v>
       </c>
@@ -20022,7 +20023,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="445" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A445" s="1" t="s">
         <v>71</v>
       </c>
@@ -20060,7 +20061,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="446" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A446" s="1" t="s">
         <v>71</v>
       </c>
@@ -20098,7 +20099,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="447" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A447" s="1" t="s">
         <v>71</v>
       </c>
@@ -20136,7 +20137,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="448" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A448" s="1" t="s">
         <v>71</v>
       </c>
@@ -20174,7 +20175,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="449" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A449" s="1" t="s">
         <v>71</v>
       </c>
@@ -20212,7 +20213,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="450" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A450" s="1" t="s">
         <v>71</v>
       </c>
@@ -20250,7 +20251,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="451" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A451" s="1" t="s">
         <v>71</v>
       </c>
@@ -20288,7 +20289,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="452" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A452" s="1" t="s">
         <v>71</v>
       </c>
@@ -20326,7 +20327,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="453" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A453" s="1" t="s">
         <v>71</v>
       </c>
@@ -20364,7 +20365,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="454" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A454" s="1" t="s">
         <v>71</v>
       </c>
@@ -20402,7 +20403,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="455" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A455" s="1" t="s">
         <v>71</v>
       </c>
@@ -20440,7 +20441,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="456" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A456" s="1" t="s">
         <v>71</v>
       </c>
@@ -20478,7 +20479,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="457" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A457" s="1" t="s">
         <v>71</v>
       </c>
@@ -20516,7 +20517,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="458" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A458" s="1" t="s">
         <v>71</v>
       </c>
@@ -20554,7 +20555,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="459" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A459" s="1" t="s">
         <v>71</v>
       </c>
@@ -20592,7 +20593,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="460" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A460" s="1" t="s">
         <v>71</v>
       </c>
@@ -20630,7 +20631,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="461" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A461" s="1" t="s">
         <v>71</v>
       </c>
@@ -20668,7 +20669,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="462" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A462" s="1" t="s">
         <v>71</v>
       </c>
@@ -20706,7 +20707,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="463" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A463" s="1" t="s">
         <v>71</v>
       </c>
@@ -20744,7 +20745,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="464" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A464" s="1" t="s">
         <v>71</v>
       </c>
@@ -20782,7 +20783,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="465" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A465" s="1" t="s">
         <v>71</v>
       </c>
@@ -20820,7 +20821,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="466" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A466" s="1" t="s">
         <v>71</v>
       </c>
@@ -20858,7 +20859,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="467" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A467" s="1" t="s">
         <v>71</v>
       </c>
@@ -20896,7 +20897,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="468" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A468" s="1" t="s">
         <v>71</v>
       </c>
@@ -20934,7 +20935,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="469" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A469" s="1" t="s">
         <v>71</v>
       </c>
@@ -20972,7 +20973,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="470" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A470" s="1" t="s">
         <v>71</v>
       </c>
@@ -21010,7 +21011,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="471" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A471" s="1" t="s">
         <v>71</v>
       </c>
@@ -21048,7 +21049,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="472" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A472" s="1" t="s">
         <v>71</v>
       </c>
@@ -21086,7 +21087,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="473" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A473" s="1" t="s">
         <v>71</v>
       </c>
@@ -21124,7 +21125,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="474" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A474" s="1" t="s">
         <v>71</v>
       </c>
@@ -21162,7 +21163,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="475" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A475" s="1" t="s">
         <v>71</v>
       </c>
@@ -21200,7 +21201,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="476" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A476" s="1" t="s">
         <v>71</v>
       </c>
@@ -21238,7 +21239,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="477" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A477" s="1" t="s">
         <v>71</v>
       </c>
@@ -21276,7 +21277,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="478" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A478" s="1" t="s">
         <v>71</v>
       </c>
@@ -21314,7 +21315,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="479" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A479" s="1" t="s">
         <v>71</v>
       </c>
@@ -21352,7 +21353,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="480" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A480" s="1" t="s">
         <v>71</v>
       </c>
@@ -21390,7 +21391,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="481" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A481" s="1" t="s">
         <v>71</v>
       </c>
@@ -21428,7 +21429,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="482" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A482" s="1" t="s">
         <v>71</v>
       </c>
@@ -21466,7 +21467,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="483" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A483" s="1" t="s">
         <v>71</v>
       </c>
@@ -21504,7 +21505,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="484" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A484" s="1" t="s">
         <v>71</v>
       </c>
@@ -21542,7 +21543,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="485" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A485" s="1" t="s">
         <v>71</v>
       </c>
@@ -21580,7 +21581,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="486" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A486" s="1" t="s">
         <v>71</v>
       </c>
@@ -21618,7 +21619,7 @@
         <v>30.6</v>
       </c>
     </row>
-    <row r="487" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A487" s="1" t="s">
         <v>71</v>
       </c>
@@ -21656,7 +21657,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="488" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A488" s="1" t="s">
         <v>71</v>
       </c>
@@ -21694,7 +21695,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="489" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A489" s="1" t="s">
         <v>71</v>
       </c>
@@ -21732,7 +21733,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="490" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A490" s="1" t="s">
         <v>71</v>
       </c>
@@ -21770,7 +21771,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="491" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A491" s="1" t="s">
         <v>71</v>
       </c>
@@ -21808,7 +21809,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="492" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A492" s="1" t="s">
         <v>71</v>
       </c>
@@ -21846,7 +21847,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="493" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A493" s="1" t="s">
         <v>71</v>
       </c>
@@ -21884,7 +21885,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="494" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A494" s="1" t="s">
         <v>71</v>
       </c>
@@ -21922,7 +21923,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="495" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A495" s="1" t="s">
         <v>71</v>
       </c>
@@ -21960,7 +21961,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="496" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A496" s="1" t="s">
         <v>71</v>
       </c>
@@ -21998,7 +21999,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="497" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A497" s="1" t="s">
         <v>71</v>
       </c>
@@ -22036,7 +22037,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="498" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A498" s="1" t="s">
         <v>71</v>
       </c>
@@ -22074,7 +22075,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="499" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A499" s="1" t="s">
         <v>71</v>
       </c>
@@ -22112,7 +22113,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="500" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A500" s="1" t="s">
         <v>71</v>
       </c>
@@ -22150,7 +22151,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="501" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A501" s="1" t="s">
         <v>71</v>
       </c>
@@ -22188,7 +22189,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="502" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A502" s="1" t="s">
         <v>71</v>
       </c>
@@ -22226,7 +22227,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="503" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A503" s="1" t="s">
         <v>71</v>
       </c>
@@ -22264,7 +22265,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="504" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A504" s="1" t="s">
         <v>71</v>
       </c>
@@ -22302,7 +22303,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="505" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A505" s="1" t="s">
         <v>71</v>
       </c>
@@ -22340,7 +22341,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="506" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A506" s="1" t="s">
         <v>71</v>
       </c>
@@ -22378,7 +22379,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="507" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A507" s="1" t="s">
         <v>71</v>
       </c>
@@ -22416,7 +22417,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="508" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A508" s="1" t="s">
         <v>71</v>
       </c>
@@ -22454,7 +22455,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="509" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A509" s="1" t="s">
         <v>71</v>
       </c>
@@ -22492,7 +22493,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="510" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A510" s="1" t="s">
         <v>71</v>
       </c>
@@ -22530,7 +22531,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="511" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A511" s="1" t="s">
         <v>71</v>
       </c>
@@ -22568,7 +22569,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="512" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A512" s="1" t="s">
         <v>71</v>
       </c>
@@ -22606,7 +22607,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="513" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A513" s="1" t="s">
         <v>71</v>
       </c>
@@ -22644,7 +22645,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="514" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A514" s="1" t="s">
         <v>71</v>
       </c>
@@ -22682,7 +22683,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="515" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A515" s="1" t="s">
         <v>71</v>
       </c>
@@ -22720,7 +22721,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="516" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A516" s="1" t="s">
         <v>71</v>
       </c>
@@ -22758,7 +22759,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="517" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A517" s="1" t="s">
         <v>71</v>
       </c>
@@ -22796,7 +22797,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="518" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A518" s="1" t="s">
         <v>71</v>
       </c>
@@ -22834,7 +22835,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="519" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A519" s="1" t="s">
         <v>71</v>
       </c>
@@ -22872,7 +22873,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="520" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A520" s="1" t="s">
         <v>71</v>
       </c>
@@ -22910,7 +22911,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="521" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A521" s="1" t="s">
         <v>71</v>
       </c>
@@ -22948,7 +22949,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="522" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A522" s="1" t="s">
         <v>71</v>
       </c>
@@ -22986,7 +22987,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="523" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A523" s="1" t="s">
         <v>71</v>
       </c>
@@ -23024,7 +23025,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="524" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A524" s="1" t="s">
         <v>71</v>
       </c>
@@ -23062,7 +23063,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="525" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A525" s="1" t="s">
         <v>71</v>
       </c>
@@ -23100,7 +23101,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="526" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A526" s="1" t="s">
         <v>71</v>
       </c>
@@ -23138,7 +23139,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="527" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A527" s="1" t="s">
         <v>71</v>
       </c>
@@ -23176,7 +23177,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="528" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A528" s="1" t="s">
         <v>71</v>
       </c>
@@ -23214,7 +23215,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="529" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A529" s="1" t="s">
         <v>71</v>
       </c>
@@ -23252,7 +23253,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="530" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A530" s="1" t="s">
         <v>71</v>
       </c>
@@ -23290,7 +23291,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="531" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A531" s="1" t="s">
         <v>71</v>
       </c>
@@ -23328,7 +23329,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="532" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A532" s="1" t="s">
         <v>71</v>
       </c>
@@ -23366,7 +23367,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="533" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A533" s="1" t="s">
         <v>71</v>
       </c>
@@ -23404,7 +23405,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="534" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A534" s="1" t="s">
         <v>71</v>
       </c>
@@ -23442,7 +23443,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="535" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A535" s="1" t="s">
         <v>71</v>
       </c>
@@ -23480,7 +23481,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="536" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A536" s="1" t="s">
         <v>71</v>
       </c>
@@ -23518,7 +23519,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="537" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A537" s="1" t="s">
         <v>71</v>
       </c>
@@ -23556,7 +23557,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="538" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A538" s="1" t="s">
         <v>71</v>
       </c>
@@ -23594,7 +23595,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="539" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F539" s="1" t="s">
         <v>27</v>
       </c>
@@ -23614,7 +23615,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="540" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F540" s="1" t="s">
         <v>682</v>
       </c>
@@ -23634,7 +23635,7 @@
         <v>2737.6</v>
       </c>
     </row>
-    <row r="541" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A541" s="1" t="s">
         <v>71</v>
       </c>
@@ -23672,7 +23673,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="542" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A542" s="1" t="s">
         <v>71</v>
       </c>
@@ -23710,7 +23711,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="543" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A543" s="1" t="s">
         <v>71</v>
       </c>
@@ -23748,7 +23749,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="544" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A544" s="1" t="s">
         <v>71</v>
       </c>
@@ -23786,7 +23787,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="545" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A545" s="1" t="s">
         <v>71</v>
       </c>
@@ -23824,7 +23825,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="546" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A546" s="1" t="s">
         <v>71</v>
       </c>
@@ -23862,7 +23863,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="547" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A547" s="1" t="s">
         <v>71</v>
       </c>
@@ -23900,7 +23901,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="548" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A548" s="1" t="s">
         <v>71</v>
       </c>
@@ -23938,7 +23939,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="549" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A549" s="1" t="s">
         <v>71</v>
       </c>
@@ -23976,7 +23977,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="550" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A550" s="1" t="s">
         <v>71</v>
       </c>
@@ -24014,7 +24015,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="551" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A551" s="1" t="s">
         <v>71</v>
       </c>
@@ -24052,7 +24053,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="552" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A552" s="1" t="s">
         <v>71</v>
       </c>
@@ -24090,7 +24091,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="553" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A553" s="1" t="s">
         <v>71</v>
       </c>
@@ -24128,7 +24129,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="554" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A554" s="1" t="s">
         <v>71</v>
       </c>
@@ -24166,7 +24167,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="555" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A555" s="1" t="s">
         <v>71</v>
       </c>
@@ -24204,7 +24205,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="556" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A556" s="1" t="s">
         <v>71</v>
       </c>
@@ -24242,7 +24243,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="557" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A557" s="1" t="s">
         <v>71</v>
       </c>
@@ -24280,7 +24281,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="558" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A558" s="1" t="s">
         <v>71</v>
       </c>
@@ -24318,7 +24319,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="559" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A559" s="1" t="s">
         <v>71</v>
       </c>
@@ -24356,7 +24357,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="560" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A560" s="1" t="s">
         <v>71</v>
       </c>
@@ -24394,7 +24395,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="561" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A561" s="1" t="s">
         <v>71</v>
       </c>
@@ -24432,7 +24433,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="562" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A562" s="1" t="s">
         <v>71</v>
       </c>
@@ -24470,7 +24471,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="563" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A563" s="1" t="s">
         <v>71</v>
       </c>
@@ -24508,7 +24509,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="564" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A564" s="1" t="s">
         <v>71</v>
       </c>
@@ -24546,7 +24547,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="565" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A565" s="1" t="s">
         <v>71</v>
       </c>
@@ -24584,7 +24585,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="566" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A566" s="1" t="s">
         <v>71</v>
       </c>
@@ -24622,7 +24623,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="567" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A567" s="1" t="s">
         <v>71</v>
       </c>
@@ -24660,7 +24661,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="568" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A568" s="1" t="s">
         <v>71</v>
       </c>
@@ -24698,7 +24699,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="569" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A569" s="1" t="s">
         <v>71</v>
       </c>
@@ -24736,7 +24737,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="570" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A570" s="1" t="s">
         <v>71</v>
       </c>
@@ -24774,7 +24775,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="571" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A571" s="1" t="s">
         <v>71</v>
       </c>
@@ -24812,7 +24813,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="572" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A572" s="1" t="s">
         <v>71</v>
       </c>
@@ -24850,7 +24851,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="573" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A573" s="1" t="s">
         <v>71</v>
       </c>
@@ -24888,7 +24889,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="574" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A574" s="1" t="s">
         <v>71</v>
       </c>
@@ -24926,7 +24927,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="575" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A575" s="1" t="s">
         <v>71</v>
       </c>
@@ -24964,7 +24965,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="576" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A576" s="1" t="s">
         <v>71</v>
       </c>
@@ -25002,7 +25003,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="577" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A577" s="1" t="s">
         <v>71</v>
       </c>
@@ -25040,7 +25041,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="578" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A578" s="1" t="s">
         <v>71</v>
       </c>
@@ -25078,7 +25079,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="579" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A579" s="1" t="s">
         <v>71</v>
       </c>
@@ -25116,7 +25117,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="580" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A580" s="1" t="s">
         <v>71</v>
       </c>
@@ -25154,7 +25155,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="581" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A581" s="1" t="s">
         <v>71</v>
       </c>
@@ -25192,7 +25193,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="582" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A582" s="1" t="s">
         <v>71</v>
       </c>
@@ -25230,7 +25231,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="583" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A583" s="1" t="s">
         <v>71</v>
       </c>
@@ -25268,7 +25269,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="584" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A584" s="1" t="s">
         <v>71</v>
       </c>
@@ -25306,7 +25307,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="585" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A585" s="1" t="s">
         <v>71</v>
       </c>
@@ -25344,7 +25345,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="586" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A586" s="1" t="s">
         <v>71</v>
       </c>
@@ -25382,7 +25383,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="587" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A587" s="1" t="s">
         <v>71</v>
       </c>
@@ -25420,7 +25421,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="588" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A588" s="1" t="s">
         <v>71</v>
       </c>
@@ -25458,7 +25459,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="589" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A589" s="1" t="s">
         <v>71</v>
       </c>
@@ -25496,7 +25497,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="590" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A590" s="1" t="s">
         <v>71</v>
       </c>
@@ -25534,7 +25535,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="591" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A591" s="1" t="s">
         <v>71</v>
       </c>
@@ -25572,7 +25573,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="592" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A592" s="1" t="s">
         <v>71</v>
       </c>
@@ -25610,7 +25611,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="593" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A593" s="1" t="s">
         <v>71</v>
       </c>
@@ -25648,7 +25649,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="594" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A594" s="1" t="s">
         <v>71</v>
       </c>
@@ -25686,7 +25687,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="595" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A595" s="1" t="s">
         <v>71</v>
       </c>
@@ -25724,7 +25725,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="596" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A596" s="1" t="s">
         <v>71</v>
       </c>
@@ -25762,7 +25763,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="597" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A597" s="1" t="s">
         <v>71</v>
       </c>
@@ -25800,7 +25801,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="598" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A598" s="1" t="s">
         <v>71</v>
       </c>
@@ -25838,7 +25839,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="599" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A599" s="1" t="s">
         <v>71</v>
       </c>
@@ -25876,7 +25877,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="600" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A600" s="1" t="s">
         <v>71</v>
       </c>
@@ -25914,7 +25915,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="601" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A601" s="1" t="s">
         <v>71</v>
       </c>
@@ -25952,7 +25953,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="602" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A602" s="1" t="s">
         <v>71</v>
       </c>
@@ -25990,7 +25991,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="603" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A603" s="1" t="s">
         <v>71</v>
       </c>
@@ -26028,7 +26029,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="604" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A604" s="1" t="s">
         <v>71</v>
       </c>
@@ -26066,7 +26067,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="605" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A605" s="1" t="s">
         <v>71</v>
       </c>
@@ -26104,7 +26105,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="606" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A606" s="1" t="s">
         <v>71</v>
       </c>
@@ -26142,7 +26143,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="607" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A607" s="1" t="s">
         <v>71</v>
       </c>
@@ -26180,7 +26181,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="608" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A608" s="1" t="s">
         <v>71</v>
       </c>
@@ -26218,7 +26219,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="609" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A609" s="1" t="s">
         <v>71</v>
       </c>
@@ -26256,7 +26257,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="610" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A610" s="1" t="s">
         <v>71</v>
       </c>
@@ -26294,7 +26295,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="611" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A611" s="1" t="s">
         <v>71</v>
       </c>
@@ -26332,7 +26333,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="612" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A612" s="1" t="s">
         <v>71</v>
       </c>
@@ -26370,7 +26371,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="613" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A613" s="1" t="s">
         <v>71</v>
       </c>
@@ -26408,7 +26409,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="614" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A614" s="1" t="s">
         <v>71</v>
       </c>
@@ -26446,7 +26447,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="615" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A615" s="1" t="s">
         <v>71</v>
       </c>
@@ -26484,7 +26485,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="616" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A616" s="1" t="s">
         <v>71</v>
       </c>
@@ -26522,7 +26523,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="617" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A617" s="1" t="s">
         <v>71</v>
       </c>
@@ -26560,7 +26561,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="618" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A618" s="1" t="s">
         <v>71</v>
       </c>
@@ -26598,7 +26599,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="619" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A619" s="1" t="s">
         <v>71</v>
       </c>
@@ -26636,7 +26637,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="620" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A620" s="1" t="s">
         <v>71</v>
       </c>
@@ -26674,7 +26675,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="621" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A621" s="1" t="s">
         <v>71</v>
       </c>
@@ -26712,7 +26713,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="622" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A622" s="1" t="s">
         <v>71</v>
       </c>
@@ -26750,7 +26751,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="623" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A623" s="1" t="s">
         <v>71</v>
       </c>
@@ -26788,7 +26789,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="624" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A624" s="1" t="s">
         <v>71</v>
       </c>
@@ -26826,7 +26827,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="625" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A625" s="1" t="s">
         <v>71</v>
       </c>
@@ -26864,7 +26865,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="626" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A626" s="1" t="s">
         <v>71</v>
       </c>
@@ -26902,7 +26903,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="627" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A627" s="1" t="s">
         <v>71</v>
       </c>
@@ -26940,7 +26941,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="628" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A628" s="1" t="s">
         <v>71</v>
       </c>
@@ -26978,7 +26979,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="629" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A629" s="1" t="s">
         <v>71</v>
       </c>
@@ -27016,7 +27017,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="630" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A630" s="1" t="s">
         <v>71</v>
       </c>
@@ -27054,7 +27055,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="631" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A631" s="1" t="s">
         <v>71</v>
       </c>
@@ -27092,7 +27093,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="632" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A632" s="1" t="s">
         <v>71</v>
       </c>
@@ -27130,7 +27131,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="633" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A633" s="1" t="s">
         <v>71</v>
       </c>
@@ -27168,7 +27169,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="634" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A634" s="1" t="s">
         <v>71</v>
       </c>
@@ -27206,7 +27207,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="635" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A635" s="1" t="s">
         <v>71</v>
       </c>
@@ -27244,7 +27245,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="636" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A636" s="1" t="s">
         <v>71</v>
       </c>
@@ -27282,7 +27283,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="637" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A637" s="1" t="s">
         <v>71</v>
       </c>
@@ -27320,7 +27321,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="638" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A638" s="1" t="s">
         <v>71</v>
       </c>
@@ -27358,7 +27359,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="639" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A639" s="1" t="s">
         <v>71</v>
       </c>
@@ -27396,7 +27397,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="640" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A640" s="1" t="s">
         <v>71</v>
       </c>
@@ -27434,7 +27435,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="641" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A641" s="1" t="s">
         <v>71</v>
       </c>
@@ -27472,7 +27473,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="642" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A642" s="1" t="s">
         <v>71</v>
       </c>
@@ -27510,7 +27511,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="643" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A643" s="1" t="s">
         <v>71</v>
       </c>
@@ -27548,7 +27549,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="644" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A644" s="1" t="s">
         <v>71</v>
       </c>
@@ -27586,7 +27587,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="645" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A645" s="1" t="s">
         <v>71</v>
       </c>
@@ -27624,7 +27625,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="646" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A646" s="1" t="s">
         <v>71</v>
       </c>
@@ -27662,7 +27663,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="647" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A647" s="1" t="s">
         <v>71</v>
       </c>
@@ -27700,7 +27701,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="648" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A648" s="1" t="s">
         <v>71</v>
       </c>
@@ -27738,7 +27739,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="649" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A649" s="1" t="s">
         <v>71</v>
       </c>
@@ -27776,7 +27777,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="650" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A650" s="1" t="s">
         <v>71</v>
       </c>
@@ -27814,7 +27815,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="651" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A651" s="1" t="s">
         <v>71</v>
       </c>
@@ -27852,7 +27853,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="652" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A652" s="1" t="s">
         <v>71</v>
       </c>
@@ -27890,7 +27891,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="653" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A653" s="1" t="s">
         <v>71</v>
       </c>
@@ -27928,7 +27929,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="654" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A654" s="1" t="s">
         <v>71</v>
       </c>
@@ -27966,7 +27967,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="655" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A655" s="1" t="s">
         <v>71</v>
       </c>
@@ -28004,7 +28005,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="656" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A656" s="1" t="s">
         <v>71</v>
       </c>
@@ -28042,7 +28043,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="657" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A657" s="1" t="s">
         <v>71</v>
       </c>
@@ -28080,7 +28081,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="658" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A658" s="1" t="s">
         <v>71</v>
       </c>
@@ -28118,7 +28119,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="659" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A659" s="1" t="s">
         <v>71</v>
       </c>
@@ -28156,7 +28157,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="660" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A660" s="1" t="s">
         <v>71</v>
       </c>
@@ -28194,7 +28195,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="661" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A661" s="1" t="s">
         <v>71</v>
       </c>
@@ -28232,7 +28233,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="662" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A662" s="1" t="s">
         <v>71</v>
       </c>
@@ -28270,7 +28271,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="663" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A663" s="1" t="s">
         <v>71</v>
       </c>
@@ -28308,7 +28309,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="664" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A664" s="1" t="s">
         <v>71</v>
       </c>
@@ -28346,7 +28347,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="665" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A665" s="1" t="s">
         <v>71</v>
       </c>
@@ -28384,7 +28385,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="666" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A666" s="1" t="s">
         <v>71</v>
       </c>
@@ -28422,7 +28423,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="667" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A667" s="1" t="s">
         <v>71</v>
       </c>
@@ -28460,7 +28461,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="668" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A668" s="1" t="s">
         <v>71</v>
       </c>
@@ -28498,7 +28499,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="669" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A669" s="1" t="s">
         <v>71</v>
       </c>
@@ -28536,7 +28537,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="670" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A670" s="1" t="s">
         <v>71</v>
       </c>
@@ -28574,7 +28575,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="671" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A671" s="1" t="s">
         <v>71</v>
       </c>
@@ -28612,7 +28613,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="672" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A672" s="1" t="s">
         <v>71</v>
       </c>
@@ -28650,7 +28651,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="673" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A673" s="1" t="s">
         <v>71</v>
       </c>
@@ -28688,7 +28689,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="674" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A674" s="1" t="s">
         <v>71</v>
       </c>
@@ -28726,7 +28727,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="675" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A675" s="1" t="s">
         <v>71</v>
       </c>
@@ -28764,7 +28765,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="676" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A676" s="1" t="s">
         <v>71</v>
       </c>
@@ -28802,7 +28803,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="677" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A677" s="1" t="s">
         <v>71</v>
       </c>
@@ -28840,7 +28841,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="678" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A678" s="1" t="s">
         <v>71</v>
       </c>
@@ -28878,7 +28879,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="679" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A679" s="1" t="s">
         <v>71</v>
       </c>
@@ -28916,7 +28917,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="680" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A680" s="1" t="s">
         <v>71</v>
       </c>
@@ -28954,7 +28955,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="681" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A681" s="1" t="s">
         <v>71</v>
       </c>
@@ -28992,7 +28993,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="682" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A682" s="1" t="s">
         <v>71</v>
       </c>
@@ -29030,7 +29031,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="683" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A683" s="1" t="s">
         <v>71</v>
       </c>
@@ -29068,7 +29069,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="684" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A684" s="1" t="s">
         <v>71</v>
       </c>
@@ -29106,7 +29107,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="685" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A685" s="1" t="s">
         <v>71</v>
       </c>
@@ -29144,7 +29145,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="686" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A686" s="1" t="s">
         <v>71</v>
       </c>
@@ -29182,7 +29183,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="687" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A687" s="1" t="s">
         <v>71</v>
       </c>
@@ -29220,7 +29221,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="688" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A688" s="1" t="s">
         <v>71</v>
       </c>
@@ -29258,7 +29259,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="689" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A689" s="1" t="s">
         <v>71</v>
       </c>
@@ -29296,7 +29297,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="690" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A690" s="1" t="s">
         <v>71</v>
       </c>
@@ -29334,7 +29335,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="691" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A691" s="1" t="s">
         <v>71</v>
       </c>
@@ -29372,7 +29373,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="692" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A692" s="1" t="s">
         <v>71</v>
       </c>
@@ -29410,7 +29411,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="693" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A693" s="1" t="s">
         <v>71</v>
       </c>
@@ -29448,7 +29449,7 @@
         <v>32.200000000000003</v>
       </c>
     </row>
-    <row r="694" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A694" s="1" t="s">
         <v>71</v>
       </c>
@@ -29486,7 +29487,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="695" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A695" s="1" t="s">
         <v>71</v>
       </c>
@@ -29524,7 +29525,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="696" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A696" s="1" t="s">
         <v>71</v>
       </c>
@@ -29562,7 +29563,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="697" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A697" s="1" t="s">
         <v>71</v>
       </c>
@@ -29600,7 +29601,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="698" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A698" s="1" t="s">
         <v>71</v>
       </c>
@@ -29638,7 +29639,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="699" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A699" s="1" t="s">
         <v>71</v>
       </c>
@@ -29676,7 +29677,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="700" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A700" s="1" t="s">
         <v>71</v>
       </c>
@@ -29714,7 +29715,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="701" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A701" s="1" t="s">
         <v>71</v>
       </c>
@@ -29752,7 +29753,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="702" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A702" s="1" t="s">
         <v>71</v>
       </c>
@@ -29790,7 +29791,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="703" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A703" s="1" t="s">
         <v>71</v>
       </c>
@@ -29828,7 +29829,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="704" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A704" s="1" t="s">
         <v>71</v>
       </c>
@@ -29866,7 +29867,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="705" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A705" s="1" t="s">
         <v>71</v>
       </c>
@@ -29904,7 +29905,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="706" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A706" s="1" t="s">
         <v>71</v>
       </c>
@@ -29942,7 +29943,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="707" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A707" s="1" t="s">
         <v>71</v>
       </c>
@@ -29980,7 +29981,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="708" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A708" s="1" t="s">
         <v>71</v>
       </c>
@@ -30018,7 +30019,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="709" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A709" s="1" t="s">
         <v>71</v>
       </c>
@@ -30056,7 +30057,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="710" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A710" s="1" t="s">
         <v>71</v>
       </c>
@@ -30094,7 +30095,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="711" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A711" s="1" t="s">
         <v>71</v>
       </c>
@@ -30132,7 +30133,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="712" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A712" s="1" t="s">
         <v>71</v>
       </c>
@@ -30170,7 +30171,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="713" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A713" s="1" t="s">
         <v>71</v>
       </c>
@@ -30208,7 +30209,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="714" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A714" s="1" t="s">
         <v>71</v>
       </c>
@@ -30246,7 +30247,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="715" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A715" s="1" t="s">
         <v>71</v>
       </c>
@@ -30284,7 +30285,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="716" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A716" s="1" t="s">
         <v>71</v>
       </c>
@@ -30322,7 +30323,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="717" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A717" s="1" t="s">
         <v>71</v>
       </c>
@@ -30360,7 +30361,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="718" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A718" s="1" t="s">
         <v>71</v>
       </c>
@@ -30398,7 +30399,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="719" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A719" s="1" t="s">
         <v>71</v>
       </c>
@@ -30436,7 +30437,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="720" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A720" s="1" t="s">
         <v>71</v>
       </c>
@@ -30474,7 +30475,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="721" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A721" s="1" t="s">
         <v>71</v>
       </c>
@@ -30512,7 +30513,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="722" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A722" s="1" t="s">
         <v>71</v>
       </c>
@@ -30550,7 +30551,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="723" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A723" s="1" t="s">
         <v>71</v>
       </c>
@@ -30588,7 +30589,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="724" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A724" s="1" t="s">
         <v>71</v>
       </c>
@@ -30626,7 +30627,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="725" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A725" s="1" t="s">
         <v>71</v>
       </c>
@@ -30664,7 +30665,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="726" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A726" s="1" t="s">
         <v>71</v>
       </c>
@@ -30702,7 +30703,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="727" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A727" s="1" t="s">
         <v>71</v>
       </c>
@@ -30740,7 +30741,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="728" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A728" s="1" t="s">
         <v>71</v>
       </c>
@@ -30778,7 +30779,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="729" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A729" s="1" t="s">
         <v>71</v>
       </c>
@@ -30816,7 +30817,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="730" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A730" s="1" t="s">
         <v>71</v>
       </c>
@@ -30854,7 +30855,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="731" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A731" s="1" t="s">
         <v>71</v>
       </c>
@@ -30892,7 +30893,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="732" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A732" s="1" t="s">
         <v>71</v>
       </c>
@@ -30930,7 +30931,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="733" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A733" s="1" t="s">
         <v>71</v>
       </c>
@@ -30968,7 +30969,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="734" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A734" s="1" t="s">
         <v>71</v>
       </c>
@@ -31006,7 +31007,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="735" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A735" s="1" t="s">
         <v>71</v>
       </c>
@@ -31044,7 +31045,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="736" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A736" s="1" t="s">
         <v>71</v>
       </c>
@@ -31082,7 +31083,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="737" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A737" s="1" t="s">
         <v>71</v>
       </c>
@@ -31120,7 +31121,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="738" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A738" s="1" t="s">
         <v>71</v>
       </c>
@@ -31158,7 +31159,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="739" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A739" s="1" t="s">
         <v>71</v>
       </c>
@@ -31196,7 +31197,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="740" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A740" s="1" t="s">
         <v>71</v>
       </c>
@@ -31234,7 +31235,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="741" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A741" s="1" t="s">
         <v>71</v>
       </c>
@@ -31272,7 +31273,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="742" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A742" s="1" t="s">
         <v>71</v>
       </c>
@@ -31310,7 +31311,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="743" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A743" s="1" t="s">
         <v>71</v>
       </c>
@@ -31348,7 +31349,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="744" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A744" s="1" t="s">
         <v>71</v>
       </c>
@@ -31386,7 +31387,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="745" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A745" s="1" t="s">
         <v>71</v>
       </c>
@@ -31424,7 +31425,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="746" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A746" s="1" t="s">
         <v>71</v>
       </c>
@@ -31462,7 +31463,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="747" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A747" s="1" t="s">
         <v>71</v>
       </c>
@@ -31500,7 +31501,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="748" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A748" s="1" t="s">
         <v>71</v>
       </c>
@@ -31538,7 +31539,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="749" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A749" s="1" t="s">
         <v>71</v>
       </c>
@@ -31576,7 +31577,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="750" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A750" s="1" t="s">
         <v>71</v>
       </c>
@@ -31614,7 +31615,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="751" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A751" s="1" t="s">
         <v>71</v>
       </c>
@@ -31652,7 +31653,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="752" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A752" s="1" t="s">
         <v>71</v>
       </c>
@@ -31690,7 +31691,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="753" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A753" s="1" t="s">
         <v>71</v>
       </c>
@@ -31728,7 +31729,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="754" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A754" s="1" t="s">
         <v>71</v>
       </c>
@@ -31766,7 +31767,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="755" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A755" s="1" t="s">
         <v>71</v>
       </c>
@@ -31804,7 +31805,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="756" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A756" s="1" t="s">
         <v>71</v>
       </c>
@@ -31842,7 +31843,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="757" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A757" s="1" t="s">
         <v>71</v>
       </c>
@@ -31880,7 +31881,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="758" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A758" s="1" t="s">
         <v>71</v>
       </c>
@@ -31918,7 +31919,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="759" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A759" s="1" t="s">
         <v>71</v>
       </c>
@@ -31956,7 +31957,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="760" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A760" s="1" t="s">
         <v>71</v>
       </c>
@@ -31994,7 +31995,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="761" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A761" s="1" t="s">
         <v>71</v>
       </c>
@@ -32032,7 +32033,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="762" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A762" s="1" t="s">
         <v>71</v>
       </c>
@@ -32070,7 +32071,7 @@
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="763" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A763" s="1" t="s">
         <v>71</v>
       </c>
@@ -32108,7 +32109,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="764" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A764" s="1" t="s">
         <v>71</v>
       </c>
@@ -32146,7 +32147,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="765" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A765" s="1" t="s">
         <v>71</v>
       </c>
@@ -32184,7 +32185,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="766" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A766" s="1" t="s">
         <v>71</v>
       </c>
@@ -32222,7 +32223,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="767" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A767" s="1" t="s">
         <v>71</v>
       </c>
@@ -32260,7 +32261,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="768" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A768" s="1" t="s">
         <v>71</v>
       </c>
@@ -32298,7 +32299,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="769" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A769" s="1" t="s">
         <v>71</v>
       </c>
@@ -32336,7 +32337,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="770" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A770" s="1" t="s">
         <v>71</v>
       </c>
@@ -32374,7 +32375,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="771" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A771" s="1" t="s">
         <v>71</v>
       </c>
@@ -32412,7 +32413,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="772" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A772" s="1" t="s">
         <v>71</v>
       </c>
@@ -32450,7 +32451,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="773" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A773" s="1" t="s">
         <v>71</v>
       </c>
@@ -32488,7 +32489,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="774" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A774" s="1" t="s">
         <v>71</v>
       </c>
@@ -32526,7 +32527,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="775" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A775" s="1" t="s">
         <v>71</v>
       </c>
@@ -32564,7 +32565,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="776" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A776" s="1" t="s">
         <v>71</v>
       </c>
@@ -32602,7 +32603,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="777" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A777" s="1" t="s">
         <v>71</v>
       </c>
@@ -32640,7 +32641,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="778" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A778" s="1" t="s">
         <v>71</v>
       </c>
@@ -32678,7 +32679,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="779" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A779" s="1" t="s">
         <v>71</v>
       </c>
@@ -32716,7 +32717,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="780" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A780" s="1" t="s">
         <v>71</v>
       </c>
@@ -32754,7 +32755,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="781" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F781" s="1" t="s">
         <v>27</v>
       </c>
@@ -32774,7 +32775,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="782" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F782" s="1" t="s">
         <v>1041</v>
       </c>
@@ -32794,7 +32795,7 @@
         <v>5631.3</v>
       </c>
     </row>
-    <row r="783" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A783" s="1" t="s">
         <v>71</v>
       </c>
@@ -32832,7 +32833,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="784" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A784" s="1" t="s">
         <v>71</v>
       </c>
@@ -32870,7 +32871,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="785" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A785" s="1" t="s">
         <v>71</v>
       </c>
@@ -32908,7 +32909,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="786" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A786" s="1" t="s">
         <v>71</v>
       </c>
@@ -32946,7 +32947,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="787" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A787" s="1" t="s">
         <v>71</v>
       </c>
@@ -32984,7 +32985,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="788" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A788" s="1" t="s">
         <v>71</v>
       </c>
@@ -33022,7 +33023,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="789" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A789" s="1" t="s">
         <v>71</v>
       </c>
@@ -33060,7 +33061,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="790" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A790" s="1" t="s">
         <v>71</v>
       </c>
@@ -33098,7 +33099,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="791" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A791" s="1" t="s">
         <v>71</v>
       </c>
@@ -33136,7 +33137,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="792" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A792" s="1" t="s">
         <v>71</v>
       </c>
@@ -33174,7 +33175,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="793" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A793" s="1" t="s">
         <v>71</v>
       </c>
@@ -33212,7 +33213,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="794" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A794" s="1" t="s">
         <v>71</v>
       </c>
@@ -33250,7 +33251,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="795" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A795" s="1" t="s">
         <v>71</v>
       </c>
@@ -33288,7 +33289,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="796" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A796" s="1" t="s">
         <v>71</v>
       </c>
@@ -33326,7 +33327,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="797" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A797" s="1" t="s">
         <v>71</v>
       </c>
@@ -33364,7 +33365,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="798" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A798" s="1" t="s">
         <v>71</v>
       </c>
@@ -33402,7 +33403,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="799" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A799" s="1" t="s">
         <v>71</v>
       </c>
@@ -33440,7 +33441,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="800" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A800" s="1" t="s">
         <v>71</v>
       </c>
@@ -33478,7 +33479,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="801" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A801" s="1" t="s">
         <v>71</v>
       </c>
@@ -33516,7 +33517,7 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="802" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A802" s="1" t="s">
         <v>71</v>
       </c>
@@ -33554,7 +33555,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="803" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A803" s="1" t="s">
         <v>71</v>
       </c>
@@ -33592,7 +33593,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="804" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A804" s="1" t="s">
         <v>71</v>
       </c>
@@ -33630,7 +33631,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="805" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F805" s="1" t="s">
         <v>27</v>
       </c>
@@ -33650,7 +33651,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="806" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F806" s="1" t="s">
         <v>412</v>
       </c>
@@ -33670,7 +33671,7 @@
         <v>477.2</v>
       </c>
     </row>
-    <row r="807" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A807" s="1" t="s">
         <v>71</v>
       </c>
@@ -33708,7 +33709,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="808" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A808" s="1" t="s">
         <v>71</v>
       </c>
@@ -33746,7 +33747,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="809" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A809" s="1" t="s">
         <v>71</v>
       </c>
@@ -33784,7 +33785,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="810" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A810" s="1" t="s">
         <v>71</v>
       </c>
@@ -33822,7 +33823,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="811" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A811" s="1" t="s">
         <v>71</v>
       </c>
@@ -33860,7 +33861,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="812" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A812" s="1" t="s">
         <v>71</v>
       </c>
@@ -33898,7 +33899,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="813" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A813" s="1" t="s">
         <v>71</v>
       </c>
@@ -33936,7 +33937,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="814" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A814" s="1" t="s">
         <v>71</v>
       </c>
@@ -33974,7 +33975,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="815" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A815" s="1" t="s">
         <v>71</v>
       </c>
@@ -34012,7 +34013,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="816" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A816" s="1" t="s">
         <v>71</v>
       </c>
@@ -34050,7 +34051,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="817" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A817" s="1" t="s">
         <v>71</v>
       </c>
@@ -34088,7 +34089,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="818" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A818" s="1" t="s">
         <v>71</v>
       </c>
@@ -34126,7 +34127,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="819" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A819" s="1" t="s">
         <v>71</v>
       </c>
@@ -34164,7 +34165,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="820" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A820" s="1" t="s">
         <v>71</v>
       </c>
@@ -34202,7 +34203,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="821" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A821" s="1" t="s">
         <v>71</v>
       </c>
@@ -34240,7 +34241,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="822" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A822" s="1" t="s">
         <v>71</v>
       </c>
@@ -34278,7 +34279,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="823" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A823" s="1" t="s">
         <v>71</v>
       </c>
@@ -34316,7 +34317,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="824" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A824" s="1" t="s">
         <v>71</v>
       </c>
@@ -34354,7 +34355,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="825" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A825" s="1" t="s">
         <v>71</v>
       </c>
@@ -34392,7 +34393,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="826" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A826" s="1" t="s">
         <v>71</v>
       </c>
@@ -34430,7 +34431,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="827" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A827" s="1" t="s">
         <v>71</v>
       </c>
@@ -34468,7 +34469,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="828" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A828" s="1" t="s">
         <v>71</v>
       </c>
@@ -34506,7 +34507,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="829" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A829" s="1" t="s">
         <v>71</v>
       </c>
@@ -34544,7 +34545,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="830" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A830" s="1" t="s">
         <v>71</v>
       </c>
@@ -34582,7 +34583,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="831" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A831" s="1" t="s">
         <v>71</v>
       </c>
@@ -34620,7 +34621,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="832" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A832" s="1" t="s">
         <v>71</v>
       </c>
@@ -34658,7 +34659,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="833" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A833" s="1" t="s">
         <v>71</v>
       </c>
@@ -34696,7 +34697,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="834" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A834" s="1" t="s">
         <v>71</v>
       </c>
@@ -34734,7 +34735,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="835" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A835" s="1" t="s">
         <v>71</v>
       </c>
@@ -34772,7 +34773,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="836" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A836" s="1" t="s">
         <v>71</v>
       </c>
@@ -34810,7 +34811,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="837" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A837" s="1" t="s">
         <v>71</v>
       </c>
@@ -34848,7 +34849,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="838" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A838" s="1" t="s">
         <v>71</v>
       </c>
@@ -34886,7 +34887,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="839" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A839" s="1" t="s">
         <v>71</v>
       </c>
@@ -34924,7 +34925,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="840" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A840" s="1" t="s">
         <v>71</v>
       </c>
@@ -34962,7 +34963,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="841" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A841" s="1" t="s">
         <v>71</v>
       </c>
@@ -35000,7 +35001,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="842" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A842" s="1" t="s">
         <v>71</v>
       </c>
@@ -35038,7 +35039,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="843" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A843" s="1" t="s">
         <v>71</v>
       </c>
@@ -35076,7 +35077,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="844" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A844" s="1" t="s">
         <v>71</v>
       </c>
@@ -35114,7 +35115,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="845" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A845" s="1" t="s">
         <v>71</v>
       </c>
@@ -35152,7 +35153,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="846" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A846" s="1" t="s">
         <v>71</v>
       </c>
@@ -35190,7 +35191,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="847" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A847" s="1" t="s">
         <v>71</v>
       </c>
@@ -35228,7 +35229,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="848" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A848" s="1" t="s">
         <v>71</v>
       </c>
@@ -35266,7 +35267,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="849" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A849" s="1" t="s">
         <v>71</v>
       </c>
@@ -35304,7 +35305,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="850" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A850" s="1" t="s">
         <v>71</v>
       </c>
@@ -35342,7 +35343,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="851" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F851" s="1" t="s">
         <v>27</v>
       </c>
@@ -35362,7 +35363,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="852" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F852" s="1" t="s">
         <v>1110</v>
       </c>
@@ -35382,7 +35383,7 @@
         <v>988.3</v>
       </c>
     </row>
-    <row r="853" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A853" s="1" t="s">
         <v>71</v>
       </c>
@@ -35420,7 +35421,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="854" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A854" s="1" t="s">
         <v>71</v>
       </c>
@@ -35458,7 +35459,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="855" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A855" s="1" t="s">
         <v>71</v>
       </c>
@@ -35496,7 +35497,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="856" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A856" s="1" t="s">
         <v>71</v>
       </c>
@@ -35534,7 +35535,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="857" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A857" s="1" t="s">
         <v>71</v>
       </c>
@@ -35572,7 +35573,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="858" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A858" s="1" t="s">
         <v>71</v>
       </c>
@@ -35610,7 +35611,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="859" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A859" s="1" t="s">
         <v>71</v>
       </c>
@@ -35648,7 +35649,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="860" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A860" s="1" t="s">
         <v>71</v>
       </c>
@@ -35686,7 +35687,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="861" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A861" s="1" t="s">
         <v>71</v>
       </c>
@@ -35724,7 +35725,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="862" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A862" s="1" t="s">
         <v>71</v>
       </c>
@@ -35762,7 +35763,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="863" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A863" s="1" t="s">
         <v>71</v>
       </c>
@@ -35800,7 +35801,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="864" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A864" s="1" t="s">
         <v>71</v>
       </c>
@@ -35838,7 +35839,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="865" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A865" s="1" t="s">
         <v>71</v>
       </c>
@@ -35876,7 +35877,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="866" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A866" s="1" t="s">
         <v>71</v>
       </c>
@@ -35914,7 +35915,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="867" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A867" s="1" t="s">
         <v>71</v>
       </c>
@@ -35952,7 +35953,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="868" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A868" s="1" t="s">
         <v>71</v>
       </c>
@@ -35990,7 +35991,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="869" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A869" s="1" t="s">
         <v>71</v>
       </c>
@@ -36028,7 +36029,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="870" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A870" s="1" t="s">
         <v>71</v>
       </c>
@@ -36066,7 +36067,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="871" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A871" s="1" t="s">
         <v>71</v>
       </c>
@@ -36104,7 +36105,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="872" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A872" s="1" t="s">
         <v>71</v>
       </c>
@@ -36142,7 +36143,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="873" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A873" s="1" t="s">
         <v>71</v>
       </c>
@@ -36180,7 +36181,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="874" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A874" s="1" t="s">
         <v>71</v>
       </c>
@@ -36218,7 +36219,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="875" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F875" s="1" t="s">
         <v>27</v>
       </c>
@@ -36238,7 +36239,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="876" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F876" s="1" t="s">
         <v>412</v>
       </c>
@@ -36258,7 +36259,7 @@
         <v>494.8</v>
       </c>
     </row>
-    <row r="877" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A877" s="1" t="s">
         <v>71</v>
       </c>
@@ -36296,7 +36297,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="878" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A878" s="1" t="s">
         <v>71</v>
       </c>
@@ -36334,7 +36335,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="879" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A879" s="1" t="s">
         <v>71</v>
       </c>
@@ -36372,7 +36373,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="880" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A880" s="1" t="s">
         <v>71</v>
       </c>
@@ -36410,7 +36411,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="881" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A881" s="1" t="s">
         <v>71</v>
       </c>
@@ -36448,7 +36449,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="882" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A882" s="1" t="s">
         <v>71</v>
       </c>
@@ -36486,7 +36487,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="883" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A883" s="1" t="s">
         <v>71</v>
       </c>
@@ -36524,7 +36525,7 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="884" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A884" s="1" t="s">
         <v>71</v>
       </c>
@@ -36562,7 +36563,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="885" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A885" s="1" t="s">
         <v>71</v>
       </c>
@@ -36600,7 +36601,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="886" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A886" s="1" t="s">
         <v>71</v>
       </c>
@@ -36638,7 +36639,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="887" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A887" s="1" t="s">
         <v>71</v>
       </c>
@@ -36676,7 +36677,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="888" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A888" s="1" t="s">
         <v>71</v>
       </c>
@@ -36714,7 +36715,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="889" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A889" s="1" t="s">
         <v>71</v>
       </c>
@@ -36752,7 +36753,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="890" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A890" s="1" t="s">
         <v>71</v>
       </c>
@@ -36790,7 +36791,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="891" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A891" s="1" t="s">
         <v>71</v>
       </c>
@@ -36828,7 +36829,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="892" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A892" s="1" t="s">
         <v>71</v>
       </c>
@@ -36866,7 +36867,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="893" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A893" s="1" t="s">
         <v>71</v>
       </c>
@@ -36904,7 +36905,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="894" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A894" s="1" t="s">
         <v>71</v>
       </c>
@@ -36942,7 +36943,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="895" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A895" s="1" t="s">
         <v>71</v>
       </c>
@@ -36980,7 +36981,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="896" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A896" s="1" t="s">
         <v>71</v>
       </c>
@@ -37018,7 +37019,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="897" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A897" s="1" t="s">
         <v>71</v>
       </c>
@@ -37056,7 +37057,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="898" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A898" s="1" t="s">
         <v>71</v>
       </c>
@@ -37094,7 +37095,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="899" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A899" s="1" t="s">
         <v>71</v>
       </c>
@@ -37132,7 +37133,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="900" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A900" s="1" t="s">
         <v>71</v>
       </c>
@@ -37170,7 +37171,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="901" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A901" s="1" t="s">
         <v>71</v>
       </c>
@@ -37208,7 +37209,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="902" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A902" s="1" t="s">
         <v>71</v>
       </c>
@@ -37246,7 +37247,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="903" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A903" s="1" t="s">
         <v>71</v>
       </c>
@@ -37284,7 +37285,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="904" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A904" s="1" t="s">
         <v>71</v>
       </c>
@@ -37322,7 +37323,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="905" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A905" s="1" t="s">
         <v>71</v>
       </c>
@@ -37360,7 +37361,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="906" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A906" s="1" t="s">
         <v>71</v>
       </c>
@@ -37398,7 +37399,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="907" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A907" s="1" t="s">
         <v>71</v>
       </c>
@@ -37436,7 +37437,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="908" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A908" s="1" t="s">
         <v>71</v>
       </c>
@@ -37474,7 +37475,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="909" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A909" s="1" t="s">
         <v>71</v>
       </c>
@@ -37512,7 +37513,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="910" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A910" s="1" t="s">
         <v>71</v>
       </c>
@@ -37550,7 +37551,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="911" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A911" s="1" t="s">
         <v>71</v>
       </c>
@@ -37588,7 +37589,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="912" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A912" s="1" t="s">
         <v>71</v>
       </c>
@@ -37626,7 +37627,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="913" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A913" s="1" t="s">
         <v>71</v>
       </c>
@@ -37664,7 +37665,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="914" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A914" s="1" t="s">
         <v>71</v>
       </c>
@@ -37702,7 +37703,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="915" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A915" s="1" t="s">
         <v>71</v>
       </c>
@@ -37740,7 +37741,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="916" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A916" s="1" t="s">
         <v>71</v>
       </c>
@@ -37778,7 +37779,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="917" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A917" s="1" t="s">
         <v>71</v>
       </c>
@@ -37816,7 +37817,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="918" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A918" s="1" t="s">
         <v>71</v>
       </c>
@@ -37854,7 +37855,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="919" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A919" s="1" t="s">
         <v>71</v>
       </c>
@@ -37892,7 +37893,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="920" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A920" s="1" t="s">
         <v>71</v>
       </c>
@@ -37930,7 +37931,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="921" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F921" s="1" t="s">
         <v>27</v>
       </c>
@@ -37950,7 +37951,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="922" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F922" s="1" t="s">
         <v>1110</v>
       </c>
@@ -37970,7 +37971,7 @@
         <v>1007.8</v>
       </c>
     </row>
-    <row r="923" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F923" s="1" t="s">
         <v>27</v>
       </c>
@@ -37990,7 +37991,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="924" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F924" s="1" t="s">
         <v>1179</v>
       </c>
@@ -38010,7 +38011,7 @@
         <v>19448.2</v>
       </c>
     </row>
-    <row r="925" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F925" s="1" t="s">
         <v>27</v>
       </c>
@@ -38030,7 +38031,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="926" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F926" s="1" t="s">
         <v>1180</v>
       </c>
@@ -38050,7 +38051,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="927" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F927" s="1" t="s">
         <v>27</v>
       </c>
@@ -38074,4 +38075,19 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D1CD41C-8AC2-4697-9904-89BC659A561D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>47529</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>